--- a/research/traditional_assets/database/data/kenya/kenya_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.101</v>
+        <v>0.0781</v>
       </c>
       <c r="E2">
-        <v>-0.0371</v>
+        <v>-0.004739999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1618673647469459</v>
+        <v>0.1763855421686747</v>
       </c>
       <c r="H2">
-        <v>0.1618673647469459</v>
+        <v>0.1763855421686747</v>
       </c>
       <c r="I2">
-        <v>0.1605584642233857</v>
+        <v>0.1855421686746988</v>
       </c>
       <c r="J2">
-        <v>0.1186373090439647</v>
+        <v>0.1368559036144578</v>
       </c>
       <c r="K2">
-        <v>26.9</v>
+        <v>27.7</v>
       </c>
       <c r="L2">
-        <v>0.1173647469458988</v>
+        <v>0.1334939759036144</v>
       </c>
       <c r="M2">
-        <v>2.56</v>
+        <v>4.75</v>
       </c>
       <c r="N2">
-        <v>0.04499121265377856</v>
+        <v>0.1144578313253012</v>
       </c>
       <c r="O2">
-        <v>0.09516728624535317</v>
+        <v>0.1714801444043321</v>
       </c>
       <c r="P2">
-        <v>2.56</v>
+        <v>4.75</v>
       </c>
       <c r="Q2">
-        <v>0.04499121265377856</v>
+        <v>0.1144578313253012</v>
       </c>
       <c r="R2">
-        <v>0.09516728624535317</v>
+        <v>0.1714801444043321</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V2">
-        <v>1.731107205623902</v>
+        <v>2.371084337349398</v>
       </c>
       <c r="W2">
-        <v>0.08531557247066285</v>
+        <v>0.08525700215450908</v>
       </c>
       <c r="X2">
-        <v>0.1511761084720616</v>
+        <v>0.2073285749937309</v>
       </c>
       <c r="Y2">
-        <v>-0.06586053600139871</v>
+        <v>-0.1220715728392218</v>
       </c>
       <c r="Z2">
-        <v>0.9447650453421268</v>
+        <v>0.8920894239036975</v>
       </c>
       <c r="AA2">
-        <v>0.1120843826581892</v>
+        <v>0.1220877042132416</v>
       </c>
       <c r="AB2">
-        <v>0.1511761084720616</v>
+        <v>0.2073285749937309</v>
       </c>
       <c r="AC2">
-        <v>-0.03909172581387231</v>
+        <v>-0.08524087078048928</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-98.5</v>
+        <v>-98.40000000000001</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>2.367788461538462</v>
+        <v>1.729349736379613</v>
       </c>
       <c r="AK2">
-        <v>-0.4553860379103097</v>
+        <v>-0.4458541005890349</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-2.654986522911051</v>
+        <v>-2.536082474226804</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.101</v>
+        <v>0.0781</v>
       </c>
       <c r="E3">
-        <v>-0.0371</v>
+        <v>-0.004739999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1618673647469459</v>
+        <v>0.1763855421686747</v>
       </c>
       <c r="H3">
-        <v>0.1618673647469459</v>
+        <v>0.1763855421686747</v>
       </c>
       <c r="I3">
-        <v>0.1605584642233857</v>
+        <v>0.1855421686746988</v>
       </c>
       <c r="J3">
-        <v>0.1186373090439647</v>
+        <v>0.1368559036144578</v>
       </c>
       <c r="K3">
-        <v>26.9</v>
+        <v>27.7</v>
       </c>
       <c r="L3">
-        <v>0.1173647469458988</v>
+        <v>0.1334939759036144</v>
       </c>
       <c r="M3">
-        <v>2.56</v>
+        <v>4.75</v>
       </c>
       <c r="N3">
-        <v>0.04499121265377856</v>
+        <v>0.1144578313253012</v>
       </c>
       <c r="O3">
-        <v>0.09516728624535317</v>
+        <v>0.1714801444043321</v>
       </c>
       <c r="P3">
-        <v>2.56</v>
+        <v>4.75</v>
       </c>
       <c r="Q3">
-        <v>0.04499121265377856</v>
+        <v>0.1144578313253012</v>
       </c>
       <c r="R3">
-        <v>0.09516728624535317</v>
+        <v>0.1714801444043321</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V3">
-        <v>1.731107205623902</v>
+        <v>2.371084337349398</v>
       </c>
       <c r="W3">
-        <v>0.08531557247066285</v>
+        <v>0.08525700215450908</v>
       </c>
       <c r="X3">
-        <v>0.1511761084720616</v>
+        <v>0.2073285749937309</v>
       </c>
       <c r="Y3">
-        <v>-0.06586053600139871</v>
+        <v>-0.1220715728392218</v>
       </c>
       <c r="Z3">
-        <v>0.9447650453421268</v>
+        <v>0.8920894239036975</v>
       </c>
       <c r="AA3">
-        <v>0.1120843826581892</v>
+        <v>0.1220877042132416</v>
       </c>
       <c r="AB3">
-        <v>0.1511761084720616</v>
+        <v>0.2073285749937309</v>
       </c>
       <c r="AC3">
-        <v>-0.03909172581387231</v>
+        <v>-0.08524087078048928</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-98.5</v>
+        <v>-98.40000000000001</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>2.367788461538462</v>
+        <v>1.729349736379613</v>
       </c>
       <c r="AK3">
-        <v>-0.4553860379103097</v>
+        <v>-0.4458541005890349</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-2.654986522911051</v>
+        <v>-2.536082474226804</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kenya/kenya_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0781</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.004739999999999999</v>
+        <v>0.00226</v>
       </c>
       <c r="G2">
-        <v>0.1763855421686747</v>
+        <v>0.1586629001883239</v>
       </c>
       <c r="H2">
-        <v>0.1763855421686747</v>
+        <v>0.1586629001883239</v>
       </c>
       <c r="I2">
-        <v>0.1855421686746988</v>
+        <v>0.1572504708097928</v>
       </c>
       <c r="J2">
-        <v>0.1368559036144578</v>
+        <v>0.1240672397383715</v>
       </c>
       <c r="K2">
-        <v>27.7</v>
+        <v>29.3</v>
       </c>
       <c r="L2">
-        <v>0.1334939759036144</v>
+        <v>0.1379472693032015</v>
       </c>
       <c r="M2">
-        <v>4.75</v>
+        <v>2.27</v>
       </c>
       <c r="N2">
-        <v>0.1144578313253012</v>
+        <v>0.06755952380952381</v>
       </c>
       <c r="O2">
-        <v>0.1714801444043321</v>
+        <v>0.07747440273037542</v>
       </c>
       <c r="P2">
-        <v>4.75</v>
+        <v>2.27</v>
       </c>
       <c r="Q2">
-        <v>0.1144578313253012</v>
+        <v>0.06755952380952381</v>
       </c>
       <c r="R2">
-        <v>0.1714801444043321</v>
+        <v>0.07747440273037542</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>98.40000000000001</v>
+        <v>107.3</v>
       </c>
       <c r="V2">
-        <v>2.371084337349398</v>
+        <v>3.193452380952381</v>
       </c>
       <c r="W2">
-        <v>0.08525700215450908</v>
+        <v>0.08941104668904486</v>
       </c>
       <c r="X2">
-        <v>0.2073285749937309</v>
+        <v>0.189803175780156</v>
       </c>
       <c r="Y2">
-        <v>-0.1220715728392218</v>
+        <v>-0.1003921290911112</v>
       </c>
       <c r="Z2">
-        <v>0.8920894239036975</v>
+        <v>0.9427430093209056</v>
       </c>
       <c r="AA2">
-        <v>0.1220877042132416</v>
+        <v>0.1169635229490906</v>
       </c>
       <c r="AB2">
-        <v>0.2073285749937309</v>
+        <v>0.189803175780156</v>
       </c>
       <c r="AC2">
-        <v>-0.08524087078048928</v>
+        <v>-0.07283965283106543</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-98.40000000000001</v>
+        <v>-107.3</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>1.729349736379613</v>
+        <v>1.455902306648575</v>
       </c>
       <c r="AK2">
-        <v>-0.4458541005890349</v>
+        <v>-0.4811659192825112</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-2.536082474226804</v>
+        <v>-3.183976261127596</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0781</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.004739999999999999</v>
+        <v>0.00226</v>
       </c>
       <c r="G3">
-        <v>0.1763855421686747</v>
+        <v>0.1586629001883239</v>
       </c>
       <c r="H3">
-        <v>0.1763855421686747</v>
+        <v>0.1586629001883239</v>
       </c>
       <c r="I3">
-        <v>0.1855421686746988</v>
+        <v>0.1572504708097928</v>
       </c>
       <c r="J3">
-        <v>0.1368559036144578</v>
+        <v>0.1240672397383715</v>
       </c>
       <c r="K3">
-        <v>27.7</v>
+        <v>29.3</v>
       </c>
       <c r="L3">
-        <v>0.1334939759036144</v>
+        <v>0.1379472693032015</v>
       </c>
       <c r="M3">
-        <v>4.75</v>
+        <v>2.27</v>
       </c>
       <c r="N3">
-        <v>0.1144578313253012</v>
+        <v>0.06755952380952381</v>
       </c>
       <c r="O3">
-        <v>0.1714801444043321</v>
+        <v>0.07747440273037542</v>
       </c>
       <c r="P3">
-        <v>4.75</v>
+        <v>2.27</v>
       </c>
       <c r="Q3">
-        <v>0.1144578313253012</v>
+        <v>0.06755952380952381</v>
       </c>
       <c r="R3">
-        <v>0.1714801444043321</v>
+        <v>0.07747440273037542</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>98.40000000000001</v>
+        <v>107.3</v>
       </c>
       <c r="V3">
-        <v>2.371084337349398</v>
+        <v>3.193452380952381</v>
       </c>
       <c r="W3">
-        <v>0.08525700215450908</v>
+        <v>0.08941104668904486</v>
       </c>
       <c r="X3">
-        <v>0.2073285749937309</v>
+        <v>0.189803175780156</v>
       </c>
       <c r="Y3">
-        <v>-0.1220715728392218</v>
+        <v>-0.1003921290911112</v>
       </c>
       <c r="Z3">
-        <v>0.8920894239036975</v>
+        <v>0.9427430093209056</v>
       </c>
       <c r="AA3">
-        <v>0.1220877042132416</v>
+        <v>0.1169635229490906</v>
       </c>
       <c r="AB3">
-        <v>0.2073285749937309</v>
+        <v>0.189803175780156</v>
       </c>
       <c r="AC3">
-        <v>-0.08524087078048928</v>
+        <v>-0.07283965283106543</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-98.40000000000001</v>
+        <v>-107.3</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.729349736379613</v>
+        <v>1.455902306648575</v>
       </c>
       <c r="AK3">
-        <v>-0.4458541005890349</v>
+        <v>-0.4811659192825112</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-2.536082474226804</v>
+        <v>-3.183976261127596</v>
       </c>
     </row>
   </sheetData>
